--- a/ITCA 2/ITCA_2026-FORMATO ORIGINAL.xlsx
+++ b/ITCA 2/ITCA_2026-FORMATO ORIGINAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\CLAUDE\ITCA 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4AB3F7-EC1D-4375-9D52-142C8222D17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7577C8EF-C1F7-45E4-A758-676D035189B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11565" yWindow="990" windowWidth="17115" windowHeight="14505" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13650" yWindow="975" windowWidth="14265" windowHeight="14505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ITCA I" sheetId="14" r:id="rId1"/>
@@ -32,6 +32,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="209">
   <si>
     <t>ACTIVIDAD ESTRATÉGICA</t>
   </si>
@@ -585,9 +587,6 @@
     <t>INFORME N 030 - 2026-ST-CODISEC/MDCH</t>
   </si>
   <si>
-    <t>INFORME N 025 - 2026-ST-CODISEC/MDCH</t>
-  </si>
-  <si>
     <t>INFORME N 026 - 2026-ST-CODISEC/MDCH</t>
   </si>
   <si>
@@ -597,15 +596,87 @@
     <t>INFORME N 022 - 2026-ST-CODISEC/MDCH</t>
   </si>
   <si>
+    <t>INFORME N 020 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
+    <t>INFORME N 021 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-INFORME N 021 - 2026-ST-CODISEC/MDCH</t>
-  </si>
-  <si>
-    <t>INFORME N 020 - 2026-ST-CODISEC/MDCH</t>
-  </si>
-  <si>
-    <t>INFORME N 023 - 2026-ST-CODISEC/MDCH
- INFORME N 024 - 2026-ST-CODISEC/MDCH</t>
+INFORME N 023 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
+    <t>INFORME N 024 - 2026-ST-CODISEC/MDCH
+ INFORME N 025 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INFORME </t>
+  </si>
+  <si>
+    <t>FECHAS</t>
+  </si>
+  <si>
+    <t>DOM5</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>VIR 31</t>
+  </si>
+  <si>
+    <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>SEPT</t>
+  </si>
+  <si>
+    <t>DOM2</t>
+  </si>
+  <si>
+    <t>VIER7</t>
+  </si>
+  <si>
+    <t>VIE28</t>
+  </si>
+  <si>
+    <t>DOM6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIE11 </t>
+  </si>
+  <si>
+    <t>VIE25</t>
+  </si>
+  <si>
+    <t>VIR 10</t>
+  </si>
+  <si>
+    <t>LISTA</t>
+  </si>
+  <si>
+    <t>ACTAS</t>
+  </si>
+  <si>
+    <t>MAPA</t>
+  </si>
+  <si>
+    <t>ACTA EXT</t>
+  </si>
+  <si>
+    <t>INFORME Nº 032 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
+    <t>INFORME Nº 033 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
+    <t>INFORME Nº 034 - 2026-ST-CODISEC/MDCH</t>
+  </si>
+  <si>
+    <t>INFORME Nº 031 - 2026-ST-CODISECMDCH</t>
+  </si>
+  <si>
+    <t>INFORME Nº 030 - 2026-ST-CODISEC/MDCH</t>
   </si>
 </sst>
 </file>
@@ -979,7 +1050,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1173,7 +1244,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1181,48 +1268,44 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1277,60 +1360,56 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1342,7 +1421,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1357,8 +1442,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1369,25 +1454,10 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1395,6 +1465,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3102,7 +3181,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6116C4E-734C-452B-98BD-F39B1CB6F420}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:V607"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3122,93 +3201,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
     </row>
     <row r="2" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="88" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="O2" s="60" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="O2" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="60"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
     </row>
     <row r="4" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="62" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="O4" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="Q4" s="64"/>
+      <c r="Q4" s="85"/>
     </row>
     <row r="5" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
     </row>
     <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="65" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="K6" s="66" t="s">
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="K6" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
       <c r="O6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="Q6" s="64"/>
+      <c r="Q6" s="85"/>
     </row>
     <row r="7" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
       <c r="O7" s="19"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="21"/>
@@ -3247,11 +3326,11 @@
       <c r="M8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="69" t="s">
+      <c r="O8" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="71"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="74"/>
       <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:22" ht="24" x14ac:dyDescent="0.25">
@@ -3282,11 +3361,11 @@
         <v>18</v>
       </c>
       <c r="M9" s="17"/>
-      <c r="O9" s="72" t="s">
+      <c r="O9" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="77"/>
     </row>
     <row r="10" spans="2:22" ht="36" x14ac:dyDescent="0.25">
       <c r="B10" s="39" t="s">
@@ -3307,11 +3386,11 @@
         <f t="shared" ref="I10:I11" si="1">IF(H10&gt;=50,"CONSIDERAR","NO")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O10" s="75" t="s">
+      <c r="O10" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="77"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="80"/>
     </row>
     <row r="11" spans="2:22" ht="48" x14ac:dyDescent="0.25">
       <c r="B11" s="39" t="s">
@@ -3334,47 +3413,47 @@
       </c>
     </row>
     <row r="12" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
       <c r="I12" s="27"/>
       <c r="O12" s="25"/>
     </row>
     <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="82"/>
+      <c r="D13" s="83" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
       <c r="I13" s="27"/>
       <c r="O13" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="P13" s="81" t="s">
+      <c r="P13" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="84"/>
+      <c r="T13" s="84"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="84"/>
     </row>
     <row r="14" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
       <c r="I14" s="27"/>
       <c r="O14" s="25"/>
     </row>
@@ -3406,11 +3485,11 @@
       <c r="O15" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="64" t="s">
+      <c r="P15" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:22" ht="24" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
@@ -3433,56 +3512,56 @@
       </c>
     </row>
     <row r="17" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="62" t="s">
+      <c r="C18" s="70"/>
+      <c r="D18" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
       <c r="I19" s="27"/>
     </row>
     <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="65" t="s">
+      <c r="C20" s="70"/>
+      <c r="D20" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
       <c r="I20" s="27"/>
     </row>
     <row r="21" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
       <c r="I21" s="27"/>
     </row>
     <row r="22" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -3876,56 +3955,56 @@
       </c>
     </row>
     <row r="36" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
       <c r="I36" s="27"/>
     </row>
     <row r="37" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="87" t="s">
+      <c r="B37" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="88" t="s">
+      <c r="C37" s="71"/>
+      <c r="D37" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="88"/>
-      <c r="F37" s="88"/>
-      <c r="G37" s="88"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
       <c r="I37" s="27"/>
     </row>
     <row r="38" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
       <c r="I38" s="27"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="65" t="s">
+      <c r="C39" s="71"/>
+      <c r="D39" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
       <c r="I39" s="27"/>
     </row>
     <row r="40" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
       <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4011,34 +4090,34 @@
       </c>
     </row>
     <row r="44" spans="2:9" s="42" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
+      <c r="B44" s="61"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
       <c r="I44" s="27"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="84"/>
-      <c r="D45" s="85" t="s">
+      <c r="C45" s="67"/>
+      <c r="D45" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="86"/>
-      <c r="F45" s="86"/>
-      <c r="G45" s="86"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
       <c r="I45" s="27"/>
     </row>
     <row r="46" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
       <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4099,47 +4178,47 @@
       <c r="I49" s="27"/>
     </row>
     <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="90" t="s">
+      <c r="B50" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="91" t="s">
+      <c r="C50" s="59"/>
+      <c r="D50" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="E50" s="91"/>
-      <c r="F50" s="91"/>
-      <c r="G50" s="91"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
       <c r="I50" s="27"/>
     </row>
     <row r="51" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="90" t="s">
+      <c r="B52" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="90"/>
-      <c r="D52" s="88" t="s">
+      <c r="C52" s="59"/>
+      <c r="D52" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
       <c r="I52" s="27"/>
     </row>
     <row r="53" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
       <c r="I53" s="27"/>
     </row>
     <row r="54" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4189,34 +4268,34 @@
       </c>
     </row>
     <row r="56" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
       <c r="I56" s="27"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="90" t="s">
+      <c r="B57" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C57" s="90"/>
-      <c r="D57" s="65" t="s">
+      <c r="C57" s="59"/>
+      <c r="D57" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="E57" s="65"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
       <c r="I57" s="27"/>
     </row>
     <row r="58" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
       <c r="I58" s="27"/>
     </row>
     <row r="59" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -4274,56 +4353,56 @@
       </c>
     </row>
     <row r="61" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
       <c r="I61" s="27"/>
     </row>
     <row r="62" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="92" t="s">
+      <c r="B62" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="92"/>
-      <c r="D62" s="88" t="s">
+      <c r="C62" s="62"/>
+      <c r="D62" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
       <c r="I62" s="27"/>
     </row>
     <row r="63" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
       <c r="I63" s="27"/>
     </row>
     <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="92" t="s">
+      <c r="B64" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="92"/>
-      <c r="D64" s="65" t="s">
+      <c r="C64" s="62"/>
+      <c r="D64" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="65"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
       <c r="I64" s="27"/>
     </row>
     <row r="65" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="56"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
       <c r="I65" s="27"/>
     </row>
     <row r="66" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4378,6 +4457,1957 @@
       <c r="I67" s="31" t="str">
         <f>IF(H67&gt;=50,"CONSIDERAR","NO")</f>
         <v>CONSIDERAR</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="57">
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="P13:V13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:G64"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H9:H11">
+    <cfRule type="cellIs" dxfId="125" priority="22" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="124" priority="23" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="123" priority="24" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="cellIs" dxfId="122" priority="19" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="121" priority="20" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="120" priority="21" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H23:H35">
+    <cfRule type="cellIs" dxfId="119" priority="16" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="118" priority="17" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="117" priority="18" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H42:H43">
+    <cfRule type="cellIs" dxfId="116" priority="13" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="115" priority="14" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="114" priority="15" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H48">
+    <cfRule type="cellIs" dxfId="113" priority="10" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="112" priority="11" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="111" priority="12" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H55">
+    <cfRule type="cellIs" dxfId="110" priority="7" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="109" priority="8" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="108" priority="9" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H60">
+    <cfRule type="cellIs" dxfId="107" priority="4" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="106" priority="5" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="105" priority="6" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H67">
+    <cfRule type="cellIs" dxfId="104" priority="1" operator="lessThan">
+      <formula>75</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="103" priority="2" operator="between">
+      <formula>75</formula>
+      <formula>94</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="102" priority="3" operator="greaterThanOrEqual">
+      <formula>95</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;CEste documento tiene carácter de Declaración Jurada</oddHeader>
+    <oddFooter>&amp;CEste documento tiene carácter de Declaración Jurada</oddFooter>
+  </headerFooter>
+  <colBreaks count="1" manualBreakCount="1">
+    <brk id="7" max="67" man="1"/>
+  </colBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B1:V607"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" style="44" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="44" customWidth="1"/>
+    <col min="3" max="4" width="25.7109375" style="44" customWidth="1"/>
+    <col min="5" max="7" width="15.7109375" style="44" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="44" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="44" hidden="1" customWidth="1"/>
+    <col min="10" max="12" width="11.42578125" style="44"/>
+    <col min="13" max="13" width="16.7109375" style="44" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" style="44"/>
+    <col min="15" max="15" width="12.28515625" style="44" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" style="44" hidden="1" customWidth="1"/>
+    <col min="17" max="22" width="11.42578125" style="44" hidden="1" customWidth="1"/>
+    <col min="23" max="16384" width="11.42578125" style="44"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+    </row>
+    <row r="2" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="88" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="O2" s="90" t="s">
+        <v>77</v>
+      </c>
+      <c r="P2" s="90"/>
+    </row>
+    <row r="3" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
+    </row>
+    <row r="4" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="89" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="89"/>
+      <c r="D4" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="O4" s="45" t="s">
+        <v>78</v>
+      </c>
+      <c r="P4" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q4" s="85"/>
+    </row>
+    <row r="5" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+    </row>
+    <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="89"/>
+      <c r="D6" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="K6" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
+      <c r="O6" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="P6" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q6" s="85"/>
+    </row>
+    <row r="7" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="21"/>
+    </row>
+    <row r="8" spans="2:22" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B8" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="L8" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="M8" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="74"/>
+      <c r="R8" s="23"/>
+    </row>
+    <row r="9" spans="2:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="F9" s="48">
+        <v>1</v>
+      </c>
+      <c r="G9" s="48">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <f>G9/F9*100</f>
+        <v>100</v>
+      </c>
+      <c r="I9" s="31" t="str">
+        <f>IF(H9&gt;=50,"CONSIDERAR","NO")</f>
+        <v>CONSIDERAR</v>
+      </c>
+      <c r="K9" s="13">
+        <f>COUNT(F9:F11)+COUNT(F16:F16)+COUNT(#REF!)+COUNT(F23:F24)+COUNT(F25)+COUNT(#REF!)+COUNT(F55:F55)+COUNT(#REF!)+COUNT(F67:F67)+COUNT(F26:F27)+COUNT(F28:F35)+COUNT(F48:F48)+COUNT(F42:F43)+COUNT(#REF!)+COUNT(#REF!)+COUNT(F60:F60)+COUNT(#REF!)</f>
+        <v>14</v>
+      </c>
+      <c r="L9" s="13">
+        <f>COUNTIF(I9:I67,"CONSIDERAR")</f>
+        <v>14</v>
+      </c>
+      <c r="M9" s="17"/>
+      <c r="O9" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="77"/>
+    </row>
+    <row r="10" spans="2:22" ht="36" x14ac:dyDescent="0.25">
+      <c r="B10" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="50"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="7" t="e">
+        <f t="shared" ref="H10:H11" si="0">G10/F10*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I10" s="31" t="e">
+        <f t="shared" ref="I10:I11" si="1">IF(H10&gt;=50,"CONSIDERAR","NO")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O10" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="80"/>
+    </row>
+    <row r="11" spans="2:22" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="48">
+        <v>1</v>
+      </c>
+      <c r="G11" s="48">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I11" s="31" t="str">
+        <f t="shared" si="1"/>
+        <v>CONSIDERAR</v>
+      </c>
+    </row>
+    <row r="12" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="I12" s="27"/>
+      <c r="O12" s="47"/>
+    </row>
+    <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="82" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="82"/>
+      <c r="D13" s="83" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="I13" s="27"/>
+      <c r="O13" s="45" t="s">
+        <v>73</v>
+      </c>
+      <c r="P13" s="84" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="84"/>
+      <c r="T13" s="84"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="84"/>
+    </row>
+    <row r="14" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="I14" s="27"/>
+      <c r="O14" s="47"/>
+    </row>
+    <row r="15" spans="2:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="O15" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="P15" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85"/>
+    </row>
+    <row r="16" spans="2:22" ht="24" x14ac:dyDescent="0.25">
+      <c r="B16" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="7" t="e">
+        <f>G16/F16*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I16" s="31" t="e">
+        <f>IF(H16&gt;=50,"CONSIDERAR","NO")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="I17" s="27"/>
+    </row>
+    <row r="18" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="70"/>
+      <c r="D18" s="86" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="I18" s="27"/>
+    </row>
+    <row r="19" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="I19" s="27"/>
+    </row>
+    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="70"/>
+      <c r="D20" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="I20" s="27"/>
+    </row>
+    <row r="21" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="I21" s="27"/>
+    </row>
+    <row r="22" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="48">
+        <v>1</v>
+      </c>
+      <c r="G23" s="48">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7">
+        <f>G23/F23*100</f>
+        <v>100</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B24" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F24" s="48">
+        <v>1</v>
+      </c>
+      <c r="G24" s="48">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" ref="H24:H35" si="2">G24/F24*100</f>
+        <v>100</v>
+      </c>
+      <c r="I24" s="31" t="str">
+        <f t="shared" ref="I24:I35" si="3">IF(H24&gt;=50,"CONSIDERAR","NO")</f>
+        <v>CONSIDERAR</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B25" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="F25" s="48">
+        <v>1</v>
+      </c>
+      <c r="G25" s="48">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="36" x14ac:dyDescent="0.25">
+      <c r="B26" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F26" s="48">
+        <v>1</v>
+      </c>
+      <c r="G26" s="48">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I26" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="B27" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="30"/>
+      <c r="E27" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I27" s="31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="48" x14ac:dyDescent="0.25">
+      <c r="B28" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="F28" s="48">
+        <v>1</v>
+      </c>
+      <c r="G28" s="48">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="36" x14ac:dyDescent="0.25">
+      <c r="B29" s="39" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="52"/>
+      <c r="E29" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I29" s="31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="36" x14ac:dyDescent="0.25">
+      <c r="B30" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="48">
+        <v>1</v>
+      </c>
+      <c r="G30" s="48">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="48" x14ac:dyDescent="0.25">
+      <c r="B31" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" s="48">
+        <v>1</v>
+      </c>
+      <c r="G31" s="48">
+        <v>1</v>
+      </c>
+      <c r="H31" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="48" x14ac:dyDescent="0.25">
+      <c r="B32" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="F32" s="48">
+        <v>1</v>
+      </c>
+      <c r="G32" s="48">
+        <v>1</v>
+      </c>
+      <c r="H32" s="7">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="B33" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="30"/>
+      <c r="E33" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I33" s="31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="B34" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="30"/>
+      <c r="E34" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I34" s="31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="48"/>
+      <c r="E35" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="7" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I35" s="31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="I36" s="27"/>
+    </row>
+    <row r="37" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="71"/>
+      <c r="D37" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="I37" s="27"/>
+    </row>
+    <row r="38" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="I38" s="27"/>
+    </row>
+    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="71"/>
+      <c r="D39" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="I39" s="27"/>
+    </row>
+    <row r="40" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" s="41" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="F42" s="48">
+        <v>3</v>
+      </c>
+      <c r="G42" s="48">
+        <v>3</v>
+      </c>
+      <c r="H42" s="7">
+        <f>G42/F42*100</f>
+        <v>100</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="41" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="E43" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" s="48">
+        <v>10</v>
+      </c>
+      <c r="G43" s="48">
+        <v>10</v>
+      </c>
+      <c r="H43" s="7">
+        <f>G43/F43*100</f>
+        <v>100</v>
+      </c>
+      <c r="I43" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="61"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
+      <c r="I44" s="27"/>
+    </row>
+    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="67"/>
+      <c r="D45" s="68" t="s">
+        <v>138</v>
+      </c>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="I45" s="27"/>
+    </row>
+    <row r="46" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="I46" s="27"/>
+    </row>
+    <row r="47" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" s="41" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" s="48">
+        <v>2</v>
+      </c>
+      <c r="G48" s="48">
+        <v>2</v>
+      </c>
+      <c r="H48" s="7">
+        <f>G48/F48*100</f>
+        <v>100</v>
+      </c>
+      <c r="I48" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I49" s="27"/>
+    </row>
+    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="59"/>
+      <c r="D50" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
+      <c r="I50" s="27"/>
+    </row>
+    <row r="51" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="I51" s="27"/>
+    </row>
+    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="59"/>
+      <c r="D52" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="I52" s="27"/>
+    </row>
+    <row r="53" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="I53" s="27"/>
+    </row>
+    <row r="54" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D54" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" s="49" customFormat="1" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="C55" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="50"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="7" t="e">
+        <f>G55/F55*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I55" s="31" t="e">
+        <f>IF(H55&gt;=50,"CONSIDERAR","NO")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
+      <c r="I56" s="27"/>
+    </row>
+    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="59"/>
+      <c r="D57" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
+      <c r="I57" s="27"/>
+    </row>
+    <row r="58" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="I58" s="27"/>
+    </row>
+    <row r="59" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="C59" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" ht="24" x14ac:dyDescent="0.25">
+      <c r="B60" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="C60" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D60" s="50"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="7" t="e">
+        <f>G60/F60*100</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I60" s="31" t="e">
+        <f>IF(H60&gt;=50,"CONSIDERAR","NO")</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
+      <c r="I61" s="27"/>
+    </row>
+    <row r="62" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="62"/>
+      <c r="D62" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="I62" s="27"/>
+    </row>
+    <row r="63" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="I63" s="27"/>
+    </row>
+    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="62" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="62"/>
+      <c r="D64" s="60" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
+      <c r="I64" s="27"/>
+    </row>
+    <row r="65" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="I65" s="27"/>
+    </row>
+    <row r="66" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="C66" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D66" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="51" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C67" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E67" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="F67" s="48">
+        <v>1</v>
+      </c>
+      <c r="G67" s="48">
+        <v>1</v>
+      </c>
+      <c r="H67" s="7">
+        <f>G67/F67*100</f>
+        <v>100</v>
+      </c>
+      <c r="I67" s="31" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4981,115 +7011,108 @@
     <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="125" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="101" priority="22" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="100" priority="23" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="24" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="99" priority="24" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="cellIs" dxfId="122" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="98" priority="19" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="121" priority="20" operator="between">
+    <cfRule type="cellIs" dxfId="97" priority="20" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="21" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="96" priority="21" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:H35">
-    <cfRule type="cellIs" dxfId="119" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="95" priority="16" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="94" priority="17" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="117" priority="18" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="93" priority="18" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42:H43">
-    <cfRule type="cellIs" dxfId="116" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="92" priority="13" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="91" priority="14" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="90" priority="15" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48">
-    <cfRule type="cellIs" dxfId="113" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="89" priority="10" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="112" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="88" priority="11" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="12" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="87" priority="12" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H55">
-    <cfRule type="cellIs" dxfId="110" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="86" priority="7" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="85" priority="8" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="108" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="84" priority="9" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="cellIs" dxfId="107" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="83" priority="4" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="82" priority="5" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H67">
-    <cfRule type="cellIs" dxfId="104" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="80" priority="1" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="79" priority="2" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="78" priority="3" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;CEste documento tiene carácter de Declaración Jurada</oddHeader>
-    <oddFooter>&amp;CEste documento tiene carácter de Declaración Jurada</oddFooter>
-  </headerFooter>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="7" max="67" man="1"/>
-  </colBreaks>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0BFA5F-F60F-4FC6-B767-D2F04386D2A6}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:V607"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5109,93 +7132,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
     </row>
     <row r="2" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="O2" s="60" t="s">
+      <c r="B2" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="O2" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="60"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
     </row>
     <row r="4" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="62" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="O4" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="Q4" s="64"/>
+      <c r="Q4" s="85"/>
     </row>
     <row r="5" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
     </row>
     <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="65" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="K6" s="66" t="s">
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="K6" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
       <c r="O6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="Q6" s="64"/>
+      <c r="Q6" s="85"/>
     </row>
     <row r="7" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
       <c r="O7" s="19"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="21"/>
@@ -5234,54 +7257,52 @@
       <c r="M8" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="69" t="s">
+      <c r="O8" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="71"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="74"/>
       <c r="R8" s="23"/>
     </row>
-    <row r="9" spans="2:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:22" ht="24" x14ac:dyDescent="0.25">
       <c r="B9" s="39" t="s">
         <v>145</v>
       </c>
       <c r="C9" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="55" t="s">
-        <v>184</v>
-      </c>
-      <c r="E9" s="32" t="s">
+      <c r="D9" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="40" t="s">
         <v>152</v>
       </c>
       <c r="F9" s="48">
         <v>1</v>
       </c>
-      <c r="G9" s="48">
-        <v>1</v>
-      </c>
+      <c r="G9" s="48"/>
       <c r="H9" s="7">
         <f>G9/F9*100</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="31" t="str">
         <f>IF(H9&gt;=50,"CONSIDERAR","NO")</f>
-        <v>CONSIDERAR</v>
+        <v>NO</v>
       </c>
       <c r="K9" s="13">
-        <f>COUNT(F9:F11)+COUNT(F16:F16)+COUNT(#REF!)+COUNT(F23:F24)+COUNT(F25)+COUNT(#REF!)+COUNT(F55:F55)+COUNT(#REF!)+COUNT(F67:F67)+COUNT(F26:F27)+COUNT(F28:F35)+COUNT(F48:F48)+COUNT(F42:F43)+COUNT(#REF!)+COUNT(#REF!)+COUNT(F60:F60)+COUNT(#REF!)</f>
-        <v>14</v>
+        <f>COUNT(F9:F11)+COUNT(F16:F16)+COUNT(#REF!)+COUNT(F23:F24)+COUNT(F25)+COUNT(#REF!)+COUNT(F55:F55)+COUNT(#REF!)+COUNT(F67:F67)+COUNT(F26:F27)+COUNT(F28:F35)+COUNT(F48:F48)+COUNT(F43)+COUNT(#REF!)+COUNT(#REF!)+COUNT(F60:F60)+COUNT(#REF!)</f>
+        <v>17</v>
       </c>
       <c r="L9" s="13">
         <f>COUNTIF(I9:I67,"CONSIDERAR")</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M9" s="17"/>
-      <c r="O9" s="72" t="s">
+      <c r="O9" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="77"/>
     </row>
     <row r="10" spans="2:22" ht="36" x14ac:dyDescent="0.25">
       <c r="B10" s="39" t="s">
@@ -5290,25 +7311,31 @@
       <c r="C10" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="48"/>
+      <c r="D10" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" s="48">
+        <v>1</v>
+      </c>
       <c r="G10" s="48"/>
-      <c r="H10" s="7" t="e">
+      <c r="H10" s="7">
         <f t="shared" ref="H10:H11" si="0">G10/F10*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I10" s="31" t="e">
+        <v>0</v>
+      </c>
+      <c r="I10" s="31" t="str">
         <f t="shared" ref="I10:I11" si="1">IF(H10&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" s="75" t="s">
+        <v>NO</v>
+      </c>
+      <c r="O10" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="77"/>
-    </row>
-    <row r="11" spans="2:22" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P10" s="79"/>
+      <c r="Q10" s="80"/>
+    </row>
+    <row r="11" spans="2:22" ht="48" x14ac:dyDescent="0.25">
       <c r="B11" s="39" t="s">
         <v>132</v>
       </c>
@@ -5316,69 +7343,97 @@
         <v>133</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>183</v>
-      </c>
-      <c r="E11" s="32" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11" s="40" t="s">
         <v>152</v>
       </c>
       <c r="F11" s="48">
         <v>1</v>
       </c>
-      <c r="G11" s="48">
-        <v>1</v>
-      </c>
+      <c r="G11" s="48"/>
       <c r="H11" s="7">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>CONSIDERAR</v>
+        <v>NO</v>
+      </c>
+      <c r="M11" s="44" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
       <c r="I12" s="27"/>
+      <c r="L12" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="N12" s="44" t="s">
+        <v>192</v>
+      </c>
       <c r="O12" s="47"/>
     </row>
     <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="82"/>
+      <c r="D13" s="83" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
       <c r="I13" s="27"/>
+      <c r="L13" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="M13" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="N13" s="44" t="s">
+        <v>196</v>
+      </c>
       <c r="O13" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="P13" s="81" t="s">
+      <c r="P13" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="84"/>
+      <c r="T13" s="84"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="84"/>
     </row>
     <row r="14" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
       <c r="I14" s="27"/>
+      <c r="L14" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="N14" s="44" t="s">
+        <v>197</v>
+      </c>
       <c r="O14" s="47"/>
     </row>
     <row r="15" spans="2:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -5406,14 +7461,23 @@
       <c r="I15" s="51" t="s">
         <v>149</v>
       </c>
+      <c r="L15" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="M15" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="N15" s="44" t="s">
+        <v>198</v>
+      </c>
       <c r="O15" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="64" t="s">
+      <c r="P15" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:22" ht="24" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
@@ -5422,73 +7486,79 @@
       <c r="C16" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="48"/>
+      <c r="D16" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="48">
+        <v>1</v>
+      </c>
       <c r="G16" s="48"/>
-      <c r="H16" s="7" t="e">
+      <c r="H16" s="7">
         <f>G16/F16*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="31" t="e">
+        <v>0</v>
+      </c>
+      <c r="I16" s="31" t="str">
         <f>IF(H16&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
       <c r="I17" s="27"/>
     </row>
-    <row r="18" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="82" t="s">
+    <row r="18" spans="2:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="62" t="s">
+      <c r="C18" s="70"/>
+      <c r="D18" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
       <c r="I18" s="27"/>
     </row>
-    <row r="19" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+    <row r="19" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
       <c r="I19" s="27"/>
     </row>
-    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="82" t="s">
+    <row r="20" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="65" t="s">
+      <c r="C20" s="70"/>
+      <c r="D20" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
       <c r="I20" s="27"/>
     </row>
-    <row r="21" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
+    <row r="21" spans="2:10" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
       <c r="I21" s="27"/>
     </row>
-    <row r="22" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="46" t="s">
         <v>0</v>
       </c>
@@ -5514,7 +7584,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="40" t="s">
         <v>94</v>
       </c>
@@ -5522,52 +7592,52 @@
         <v>122</v>
       </c>
       <c r="D23" s="30" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F23" s="48">
-        <v>1</v>
-      </c>
-      <c r="G23" s="48">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G23" s="48"/>
       <c r="H23" s="7">
         <f>G23/F23*100</f>
-        <v>100</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I23" s="31" t="str">
+        <f>IF(H23&gt;=50,"CONSIDERAR","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J23" s="56"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
         <v>96</v>
       </c>
       <c r="C24" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="D24" s="30"/>
+      <c r="D24" s="30" t="s">
+        <v>201</v>
+      </c>
       <c r="E24" s="36" t="s">
         <v>97</v>
       </c>
       <c r="F24" s="48">
         <v>1</v>
       </c>
-      <c r="G24" s="48">
-        <v>1</v>
-      </c>
+      <c r="G24" s="48"/>
       <c r="H24" s="7">
         <f t="shared" ref="H24:H35" si="2">G24/F24*100</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="31" t="str">
         <f t="shared" ref="I24:I35" si="3">IF(H24&gt;=50,"CONSIDERAR","NO")</f>
-        <v>CONSIDERAR</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
         <v>98</v>
       </c>
@@ -5575,26 +7645,25 @@
         <v>123</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="F25" s="48">
         <v>1</v>
       </c>
-      <c r="G25" s="48">
-        <v>1</v>
-      </c>
+      <c r="G25" s="48"/>
       <c r="H25" s="7">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="36" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I25" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="36" x14ac:dyDescent="0.25">
       <c r="B26" s="39" t="s">
         <v>99</v>
       </c>
@@ -5602,7 +7671,7 @@
         <v>124</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>100</v>
@@ -5610,18 +7679,17 @@
       <c r="F26" s="48">
         <v>1</v>
       </c>
-      <c r="G26" s="48">
-        <v>1</v>
-      </c>
+      <c r="G26" s="48"/>
       <c r="H26" s="7">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I26" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="24" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I26" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" ht="24" x14ac:dyDescent="0.25">
       <c r="B27" s="39" t="s">
         <v>101</v>
       </c>
@@ -5629,9 +7697,7 @@
         <v>122</v>
       </c>
       <c r="D27" s="30"/>
-      <c r="E27" s="36" t="s">
-        <v>97</v>
-      </c>
+      <c r="E27" s="36"/>
       <c r="F27" s="48"/>
       <c r="G27" s="48"/>
       <c r="H27" s="7" t="e">
@@ -5643,7 +7709,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="48" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" ht="48" x14ac:dyDescent="0.25">
       <c r="B28" s="39" t="s">
         <v>102</v>
       </c>
@@ -5651,26 +7717,25 @@
         <v>125</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="F28" s="48">
         <v>1</v>
       </c>
-      <c r="G28" s="48">
-        <v>1</v>
-      </c>
+      <c r="G28" s="48"/>
       <c r="H28" s="7">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I28" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="36" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I28" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="36" x14ac:dyDescent="0.25">
       <c r="B29" s="39" t="s">
         <v>103</v>
       </c>
@@ -5678,9 +7743,7 @@
         <v>126</v>
       </c>
       <c r="D29" s="52"/>
-      <c r="E29" s="36" t="s">
-        <v>104</v>
-      </c>
+      <c r="E29" s="36"/>
       <c r="F29" s="48"/>
       <c r="G29" s="48"/>
       <c r="H29" s="7" t="e">
@@ -5692,34 +7755,27 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="36" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" ht="36" x14ac:dyDescent="0.25">
       <c r="B30" s="39" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="D30" s="52" t="s">
-        <v>176</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="F30" s="48">
-        <v>1</v>
-      </c>
-      <c r="G30" s="48">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7">
+      <c r="D30" s="52"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="7" t="e">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I30" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="48" x14ac:dyDescent="0.25">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I30" s="31" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="48" x14ac:dyDescent="0.25">
       <c r="B31" s="39" t="s">
         <v>107</v>
       </c>
@@ -5727,7 +7783,7 @@
         <v>126</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>150</v>
@@ -5735,18 +7791,17 @@
       <c r="F31" s="48">
         <v>1</v>
       </c>
-      <c r="G31" s="48">
-        <v>1</v>
-      </c>
+      <c r="G31" s="48"/>
       <c r="H31" s="7">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I31" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="48" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="I31" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="48" x14ac:dyDescent="0.25">
       <c r="B32" s="39" t="s">
         <v>108</v>
       </c>
@@ -5754,7 +7809,7 @@
         <v>126</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="E32" s="36" t="s">
         <v>106</v>
@@ -5762,15 +7817,14 @@
       <c r="F32" s="48">
         <v>1</v>
       </c>
-      <c r="G32" s="48">
-        <v>1</v>
-      </c>
+      <c r="G32" s="48"/>
       <c r="H32" s="7">
         <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="I32" s="31" t="s">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="31" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="24" x14ac:dyDescent="0.25">
@@ -5780,19 +7834,23 @@
       <c r="C33" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="30"/>
+      <c r="D33" s="30" t="s">
+        <v>202</v>
+      </c>
       <c r="E33" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="48"/>
+      <c r="F33" s="48">
+        <v>1</v>
+      </c>
       <c r="G33" s="48"/>
-      <c r="H33" s="7" t="e">
+      <c r="H33" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I33" s="31" t="e">
+        <v>0</v>
+      </c>
+      <c r="I33" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="24" x14ac:dyDescent="0.25">
@@ -5802,19 +7860,23 @@
       <c r="C34" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="30"/>
+      <c r="D34" s="30" t="s">
+        <v>202</v>
+      </c>
       <c r="E34" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="F34" s="48"/>
+      <c r="F34" s="48">
+        <v>1</v>
+      </c>
       <c r="G34" s="48"/>
-      <c r="H34" s="7" t="e">
+      <c r="H34" s="7">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="31" t="e">
+        <v>0</v>
+      </c>
+      <c r="I34" s="31" t="str">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
@@ -5825,9 +7887,7 @@
         <v>122</v>
       </c>
       <c r="D35" s="48"/>
-      <c r="E35" s="36" t="s">
-        <v>114</v>
-      </c>
+      <c r="E35" s="36"/>
       <c r="F35" s="48"/>
       <c r="G35" s="48"/>
       <c r="H35" s="7" t="e">
@@ -5840,56 +7900,56 @@
       </c>
     </row>
     <row r="36" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
       <c r="I36" s="27"/>
     </row>
     <row r="37" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="87" t="s">
+      <c r="B37" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="91" t="s">
+      <c r="C37" s="71"/>
+      <c r="D37" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="91"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
       <c r="I37" s="27"/>
     </row>
     <row r="38" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
       <c r="I38" s="27"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="65" t="s">
+      <c r="C39" s="71"/>
+      <c r="D39" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
       <c r="I39" s="27"/>
     </row>
     <row r="40" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
       <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5926,26 +7986,25 @@
         <v>127</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="E42" s="32" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F42" s="48">
         <v>3</v>
       </c>
-      <c r="G42" s="48">
-        <v>3</v>
-      </c>
+      <c r="G42" s="48"/>
       <c r="H42" s="7">
         <f>G42/F42*100</f>
-        <v>100</v>
-      </c>
-      <c r="I42" s="31" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" s="41" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="31" t="str">
+        <f>IF(H42&gt;=50,"CONSIDERAR","NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" s="41" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="40" t="s">
         <v>151</v>
       </c>
@@ -5953,54 +8012,53 @@
         <v>127</v>
       </c>
       <c r="D43" s="30" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="E43" s="32" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F43" s="48">
         <v>10</v>
       </c>
-      <c r="G43" s="48">
-        <v>10</v>
-      </c>
+      <c r="G43" s="48"/>
       <c r="H43" s="7">
         <f>G43/F43*100</f>
-        <v>100</v>
-      </c>
-      <c r="I43" s="31" t="s">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="31" t="str">
+        <f>IF(H43&gt;=50,"CONSIDERAR","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
+      <c r="B44" s="61"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
       <c r="I44" s="27"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="84"/>
-      <c r="D45" s="85" t="s">
+      <c r="C45" s="67"/>
+      <c r="D45" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="86"/>
-      <c r="F45" s="86"/>
-      <c r="G45" s="86"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
       <c r="I45" s="27"/>
     </row>
     <row r="46" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
       <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -6029,7 +8087,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="41" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:9" s="41" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="39" t="s">
         <v>119</v>
       </c>
@@ -6037,7 +8095,7 @@
         <v>128</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="E48" s="33" t="s">
         <v>97</v>
@@ -6045,62 +8103,61 @@
       <c r="F48" s="48">
         <v>2</v>
       </c>
-      <c r="G48" s="48">
-        <v>2</v>
-      </c>
+      <c r="G48" s="48"/>
       <c r="H48" s="7">
         <f>G48/F48*100</f>
-        <v>100</v>
-      </c>
-      <c r="I48" s="31" t="s">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="I48" s="31" t="str">
+        <f>IF(H48&gt;=50,"CONSIDERAR","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="49" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I49" s="27"/>
     </row>
     <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="90" t="s">
+      <c r="B50" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="91" t="s">
+      <c r="C50" s="59"/>
+      <c r="D50" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="E50" s="91"/>
-      <c r="F50" s="91"/>
-      <c r="G50" s="91"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
       <c r="I50" s="27"/>
     </row>
     <row r="51" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="90" t="s">
+      <c r="B52" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="90"/>
-      <c r="D52" s="88" t="s">
+      <c r="C52" s="59"/>
+      <c r="D52" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
       <c r="I52" s="27"/>
     </row>
     <row r="53" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
       <c r="I53" s="27"/>
     </row>
     <row r="54" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -6136,48 +8193,54 @@
       <c r="C55" s="40" t="s">
         <v>148</v>
       </c>
-      <c r="D55" s="50"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="30"/>
+      <c r="D55" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="E55" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="F55" s="30">
+        <v>1</v>
+      </c>
       <c r="G55" s="30"/>
-      <c r="H55" s="7" t="e">
+      <c r="H55" s="7">
         <f>G55/F55*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="31" t="e">
+        <v>0</v>
+      </c>
+      <c r="I55" s="31" t="str">
         <f>IF(H55&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
+        <v>NO</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
       <c r="I56" s="27"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="90" t="s">
+      <c r="B57" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C57" s="90"/>
-      <c r="D57" s="65" t="s">
+      <c r="C57" s="59"/>
+      <c r="D57" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="E57" s="65"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
       <c r="I57" s="27"/>
     </row>
     <row r="58" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
       <c r="I58" s="27"/>
     </row>
     <row r="59" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -6227,56 +8290,56 @@
       </c>
     </row>
     <row r="61" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
       <c r="I61" s="27"/>
     </row>
     <row r="62" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="92" t="s">
+      <c r="B62" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="92"/>
-      <c r="D62" s="88" t="s">
+      <c r="C62" s="62"/>
+      <c r="D62" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
       <c r="I62" s="27"/>
     </row>
     <row r="63" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
       <c r="I63" s="27"/>
     </row>
     <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="92" t="s">
+      <c r="B64" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="92"/>
-      <c r="D64" s="65" t="s">
+      <c r="C64" s="62"/>
+      <c r="D64" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="65"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
       <c r="I64" s="27"/>
     </row>
     <row r="65" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="56"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
       <c r="I65" s="27"/>
     </row>
     <row r="66" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -6305,7 +8368,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="67" spans="2:9" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:9" ht="72" x14ac:dyDescent="0.25">
       <c r="B67" s="40" t="s">
         <v>121</v>
       </c>
@@ -6313,23 +8376,22 @@
         <v>129</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="E67" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="E67" s="40" t="s">
         <v>152</v>
       </c>
       <c r="F67" s="48">
         <v>1</v>
       </c>
-      <c r="G67" s="48">
-        <v>1</v>
-      </c>
+      <c r="G67" s="48"/>
       <c r="H67" s="7">
         <f>G67/F67*100</f>
-        <v>100</v>
-      </c>
-      <c r="I67" s="31" t="s">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="I67" s="31" t="str">
+        <f>IF(H67&gt;=50,"CONSIDERAR","NO")</f>
+        <v>NO</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6874,6 +8936,50 @@
     <row r="607" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="P13:V13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B2:G2"/>
@@ -6887,153 +8993,110 @@
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="P13:V13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:G64"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="101" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="77" priority="22" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="76" priority="23" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="99" priority="24" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="75" priority="24" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H16">
-    <cfRule type="cellIs" dxfId="98" priority="19" operator="lessThan">
+    <cfRule type="cellIs" dxfId="74" priority="19" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="20" operator="between">
+    <cfRule type="cellIs" dxfId="73" priority="20" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="21" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="72" priority="21" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H23:H35">
-    <cfRule type="cellIs" dxfId="95" priority="16" operator="lessThan">
+    <cfRule type="cellIs" dxfId="71" priority="16" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="70" priority="17" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="18" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="69" priority="18" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42:H43">
-    <cfRule type="cellIs" dxfId="92" priority="13" operator="lessThan">
+    <cfRule type="cellIs" dxfId="68" priority="13" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="67" priority="14" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="66" priority="15" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48">
-    <cfRule type="cellIs" dxfId="89" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="65" priority="10" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="64" priority="11" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="87" priority="12" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="63" priority="12" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H55">
-    <cfRule type="cellIs" dxfId="86" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="61" priority="8" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H60">
-    <cfRule type="cellIs" dxfId="83" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="59" priority="4" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="58" priority="5" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="81" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="57" priority="6" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H67">
-    <cfRule type="cellIs" dxfId="80" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="56" priority="1" operator="lessThan">
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="2" operator="between">
+    <cfRule type="cellIs" dxfId="55" priority="2" operator="between">
       <formula>75</formula>
       <formula>94</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="54" priority="3" operator="greaterThanOrEqual">
       <formula>95</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB2CCDDB-85CD-47F9-80E4-DEEA939A9EA5}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:V607"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7053,93 +9116,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
     </row>
     <row r="2" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="O2" s="60" t="s">
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="O2" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="P2" s="60"/>
+      <c r="P2" s="90"/>
     </row>
     <row r="3" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="91"/>
+      <c r="G3" s="91"/>
     </row>
     <row r="4" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="62" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="86" t="s">
         <v>144</v>
       </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
       <c r="O4" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="P4" s="64" t="s">
+      <c r="P4" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="Q4" s="64"/>
+      <c r="Q4" s="85"/>
     </row>
     <row r="5" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
     </row>
     <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="65" t="s">
+      <c r="C6" s="89"/>
+      <c r="D6" s="60" t="s">
         <v>136</v>
       </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="K6" s="66" t="s">
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="K6" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
       <c r="O6" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="Q6" s="64"/>
+      <c r="Q6" s="85"/>
     </row>
     <row r="7" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
       <c r="O7" s="19"/>
       <c r="P7" s="20"/>
       <c r="Q7" s="21"/>
@@ -7178,11 +9241,11 @@
       <c r="M8" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="69" t="s">
+      <c r="O8" s="72" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="71"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="74"/>
       <c r="R8" s="23"/>
     </row>
     <row r="9" spans="2:22" ht="24" x14ac:dyDescent="0.25">
@@ -7213,11 +9276,11 @@
         <v>0</v>
       </c>
       <c r="M9" s="17"/>
-      <c r="O9" s="72" t="s">
+      <c r="O9" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="77"/>
     </row>
     <row r="10" spans="2:22" ht="36" x14ac:dyDescent="0.25">
       <c r="B10" s="39" t="s">
@@ -7238,11 +9301,11 @@
         <f t="shared" ref="I10:I11" si="1">IF(H10&gt;=50,"CONSIDERAR","NO")</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O10" s="75" t="s">
+      <c r="O10" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="77"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="80"/>
     </row>
     <row r="11" spans="2:22" ht="48" x14ac:dyDescent="0.25">
       <c r="B11" s="39" t="s">
@@ -7265,47 +9328,47 @@
       </c>
     </row>
     <row r="12" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
       <c r="I12" s="27"/>
       <c r="O12" s="47"/>
     </row>
     <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="79" t="s">
+      <c r="B13" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80" t="s">
+      <c r="C13" s="82"/>
+      <c r="D13" s="83" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
       <c r="I13" s="27"/>
       <c r="O13" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="P13" s="81" t="s">
+      <c r="P13" s="84" t="s">
         <v>75</v>
       </c>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
+      <c r="S13" s="84"/>
+      <c r="T13" s="84"/>
+      <c r="U13" s="84"/>
+      <c r="V13" s="84"/>
     </row>
     <row r="14" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
       <c r="I14" s="27"/>
       <c r="O14" s="47"/>
     </row>
@@ -7337,11 +9400,11 @@
       <c r="O15" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="P15" s="64" t="s">
+      <c r="P15" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:22" ht="24" x14ac:dyDescent="0.25">
       <c r="B16" s="40" t="s">
@@ -7364,56 +9427,56 @@
       </c>
     </row>
     <row r="17" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
       <c r="I17" s="27"/>
     </row>
     <row r="18" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="82" t="s">
+      <c r="B18" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="62" t="s">
+      <c r="C18" s="70"/>
+      <c r="D18" s="86" t="s">
         <v>92</v>
       </c>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
       <c r="I19" s="27"/>
     </row>
     <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="82" t="s">
+      <c r="B20" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="65" t="s">
+      <c r="C20" s="70"/>
+      <c r="D20" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
       <c r="I20" s="27"/>
     </row>
     <row r="21" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
       <c r="I21" s="27"/>
     </row>
     <row r="22" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -7729,56 +9792,56 @@
       </c>
     </row>
     <row r="36" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
       <c r="I36" s="27"/>
     </row>
     <row r="37" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="87" t="s">
+      <c r="B37" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="91" t="s">
+      <c r="C37" s="71"/>
+      <c r="D37" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="E37" s="91"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
       <c r="I37" s="27"/>
     </row>
     <row r="38" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
       <c r="I38" s="27"/>
     </row>
     <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="65" t="s">
+      <c r="C39" s="71"/>
+      <c r="D39" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
       <c r="I39" s="27"/>
     </row>
     <row r="40" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
       <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7848,34 +9911,34 @@
       </c>
     </row>
     <row r="44" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
+      <c r="B44" s="61"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="61"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="61"/>
+      <c r="G44" s="61"/>
       <c r="I44" s="27"/>
     </row>
     <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="83" t="s">
+      <c r="B45" s="66" t="s">
         <v>87</v>
       </c>
-      <c r="C45" s="84"/>
-      <c r="D45" s="85" t="s">
+      <c r="C45" s="67"/>
+      <c r="D45" s="68" t="s">
         <v>138</v>
       </c>
-      <c r="E45" s="86"/>
-      <c r="F45" s="86"/>
-      <c r="G45" s="86"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
       <c r="I45" s="27"/>
     </row>
     <row r="46" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
       <c r="I46" s="27"/>
     </row>
     <row r="47" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7928,47 +9991,47 @@
       <c r="I49" s="27"/>
     </row>
     <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="90" t="s">
+      <c r="B50" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="91" t="s">
+      <c r="C50" s="59"/>
+      <c r="D50" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="E50" s="91"/>
-      <c r="F50" s="91"/>
-      <c r="G50" s="91"/>
+      <c r="E50" s="65"/>
+      <c r="F50" s="65"/>
+      <c r="G50" s="65"/>
       <c r="I50" s="27"/>
     </row>
     <row r="51" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
       <c r="I51" s="27"/>
     </row>
     <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="90" t="s">
+      <c r="B52" s="59" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="90"/>
-      <c r="D52" s="88" t="s">
+      <c r="C52" s="59"/>
+      <c r="D52" s="63" t="s">
         <v>146</v>
       </c>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
       <c r="I52" s="27"/>
     </row>
     <row r="53" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
       <c r="I53" s="27"/>
     </row>
     <row r="54" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8018,34 +10081,34 @@
       </c>
     </row>
     <row r="56" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
       <c r="I56" s="27"/>
     </row>
     <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="90" t="s">
+      <c r="B57" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="C57" s="90"/>
-      <c r="D57" s="65" t="s">
+      <c r="C57" s="59"/>
+      <c r="D57" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="E57" s="65"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
       <c r="I57" s="27"/>
     </row>
     <row r="58" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
       <c r="I58" s="27"/>
     </row>
     <row r="59" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8095,56 +10158,56 @@
       </c>
     </row>
     <row r="61" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="61"/>
+      <c r="D61" s="61"/>
+      <c r="E61" s="61"/>
+      <c r="F61" s="61"/>
+      <c r="G61" s="61"/>
       <c r="I61" s="27"/>
     </row>
     <row r="62" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="92" t="s">
+      <c r="B62" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="92"/>
-      <c r="D62" s="88" t="s">
+      <c r="C62" s="62"/>
+      <c r="D62" s="63" t="s">
         <v>142</v>
       </c>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
       <c r="I62" s="27"/>
     </row>
     <row r="63" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
       <c r="I63" s="27"/>
     </row>
     <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="92" t="s">
+      <c r="B64" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="92"/>
-      <c r="D64" s="65" t="s">
+      <c r="C64" s="62"/>
+      <c r="D64" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="65"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
       <c r="I64" s="27"/>
     </row>
     <row r="65" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="56"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
       <c r="I65" s="27"/>
     </row>
     <row r="66" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -8735,6 +10798,50 @@
     <row r="607" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="B65:G65"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="P13:V13"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="P15:R15"/>
+    <mergeCell ref="B17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B2:G2"/>
@@ -8748,1911 +10855,6 @@
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="P13:V13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:G64"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H9:H11">
-    <cfRule type="cellIs" dxfId="77" priority="22" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="23" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="75" priority="24" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="cellIs" dxfId="74" priority="19" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="20" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="21" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23:H35">
-    <cfRule type="cellIs" dxfId="71" priority="16" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="17" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="18" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H42:H43">
-    <cfRule type="cellIs" dxfId="68" priority="13" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="14" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="15" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H48">
-    <cfRule type="cellIs" dxfId="65" priority="10" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="11" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="63" priority="12" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H55">
-    <cfRule type="cellIs" dxfId="62" priority="7" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="8" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="9" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H60">
-    <cfRule type="cellIs" dxfId="59" priority="4" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="5" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="6" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H67">
-    <cfRule type="cellIs" dxfId="56" priority="1" operator="lessThan">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="2" operator="between">
-      <formula>75</formula>
-      <formula>94</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="3" operator="greaterThanOrEqual">
-      <formula>95</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{263EFEC4-60AB-4E50-B3B4-C157FCCBE27E}">
-  <dimension ref="B1:V607"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.7109375" style="44" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="44" customWidth="1"/>
-    <col min="3" max="4" width="25.7109375" style="44" customWidth="1"/>
-    <col min="5" max="7" width="15.7109375" style="44" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="44" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" style="44" hidden="1" customWidth="1"/>
-    <col min="10" max="12" width="11.42578125" style="44"/>
-    <col min="13" max="13" width="16.7109375" style="44" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="44"/>
-    <col min="15" max="15" width="12.28515625" style="44" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="11.85546875" style="44" hidden="1" customWidth="1"/>
-    <col min="17" max="22" width="11.42578125" style="44" hidden="1" customWidth="1"/>
-    <col min="23" max="16384" width="11.42578125" style="44"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-    </row>
-    <row r="2" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="O2" s="60" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" s="60"/>
-    </row>
-    <row r="3" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-    </row>
-    <row r="4" spans="2:22" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="59"/>
-      <c r="D4" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="O4" s="45" t="s">
-        <v>78</v>
-      </c>
-      <c r="P4" s="64" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q4" s="64"/>
-    </row>
-    <row r="5" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="61"/>
-      <c r="E5" s="61"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="61"/>
-    </row>
-    <row r="6" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="59" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="59"/>
-      <c r="D6" s="65" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="K6" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
-      <c r="O6" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="P6" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q6" s="64"/>
-    </row>
-    <row r="7" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="56"/>
-      <c r="C7" s="56"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="21"/>
-    </row>
-    <row r="8" spans="2:22" s="49" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I8" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="K8" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="L8" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="P8" s="70"/>
-      <c r="Q8" s="71"/>
-      <c r="R8" s="23"/>
-    </row>
-    <row r="9" spans="2:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="B9" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="50"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="7" t="e">
-        <f>G9/F9*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I9" s="31" t="e">
-        <f>IF(H9&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K9" s="13">
-        <f>COUNT(F9:F11)+COUNT(F16:F16)+COUNT(#REF!)+COUNT(F23:F24)+COUNT(F25)+COUNT(#REF!)+COUNT(F55:F55)+COUNT(#REF!)+COUNT(F67:F67)+COUNT(F26:F27)+COUNT(F28:F35)+COUNT(F48:F48)+COUNT(F43)+COUNT(#REF!)+COUNT(#REF!)+COUNT(F60:F60)+COUNT(#REF!)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="13">
-        <f>COUNTIF(I9:I67,"CONSIDERAR")</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="17"/>
-      <c r="O9" s="72" t="s">
-        <v>83</v>
-      </c>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74"/>
-    </row>
-    <row r="10" spans="2:22" ht="36" x14ac:dyDescent="0.25">
-      <c r="B10" s="39" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="48"/>
-      <c r="G10" s="48"/>
-      <c r="H10" s="7" t="e">
-        <f t="shared" ref="H10:H11" si="0">G10/F10*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I10" s="31" t="e">
-        <f t="shared" ref="I10:I11" si="1">IF(H10&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O10" s="75" t="s">
-        <v>82</v>
-      </c>
-      <c r="P10" s="76"/>
-      <c r="Q10" s="77"/>
-    </row>
-    <row r="11" spans="2:22" ht="48" x14ac:dyDescent="0.25">
-      <c r="B11" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="D11" s="50"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="7" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I11" s="31" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="78"/>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="78"/>
-      <c r="I12" s="27"/>
-      <c r="O12" s="47"/>
-    </row>
-    <row r="13" spans="2:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="79" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="80"/>
-      <c r="I13" s="27"/>
-      <c r="O13" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="P13" s="81" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="81"/>
-      <c r="T13" s="81"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-    </row>
-    <row r="14" spans="2:22" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
-      <c r="I14" s="27"/>
-      <c r="O14" s="47"/>
-    </row>
-    <row r="15" spans="2:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="H15" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="O15" s="45" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="64"/>
-      <c r="R15" s="64"/>
-    </row>
-    <row r="16" spans="2:22" ht="24" x14ac:dyDescent="0.25">
-      <c r="B16" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="50"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="7" t="e">
-        <f>G16/F16*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="31" t="e">
-        <f>IF(H16&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="56"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="I17" s="27"/>
-    </row>
-    <row r="18" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="82"/>
-      <c r="D18" s="62" t="s">
-        <v>92</v>
-      </c>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="I18" s="27"/>
-    </row>
-    <row r="19" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="I19" s="27"/>
-    </row>
-    <row r="20" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="82" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" s="65"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="I20" s="27"/>
-    </row>
-    <row r="21" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="I21" s="27"/>
-    </row>
-    <row r="22" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H22" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="7" t="e">
-        <f>G23/F23*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I23" s="31" t="e">
-        <f>IF(H23&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="30"/>
-      <c r="E24" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="7" t="e">
-        <f t="shared" ref="H24:H35" si="2">G24/F24*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I24" s="31" t="e">
-        <f t="shared" ref="I24:I35" si="3">IF(H24&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I25" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="36" x14ac:dyDescent="0.25">
-      <c r="B26" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I26" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="B27" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" s="30"/>
-      <c r="E27" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I27" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" ht="48" x14ac:dyDescent="0.25">
-      <c r="B28" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="30"/>
-      <c r="E28" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I28" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" ht="36" x14ac:dyDescent="0.25">
-      <c r="B29" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="52"/>
-      <c r="E29" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I29" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" ht="36" x14ac:dyDescent="0.25">
-      <c r="B30" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="52"/>
-      <c r="E30" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="F30" s="48"/>
-      <c r="G30" s="48"/>
-      <c r="H30" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I30" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="48" x14ac:dyDescent="0.25">
-      <c r="B31" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="52"/>
-      <c r="E31" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I31" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" ht="48" x14ac:dyDescent="0.25">
-      <c r="B32" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="36" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I32" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="B33" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="30"/>
-      <c r="E33" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I33" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="B34" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="48"/>
-      <c r="E35" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="7" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I35" s="31" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="36" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="56"/>
-      <c r="G36" s="56"/>
-      <c r="I36" s="27"/>
-    </row>
-    <row r="37" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="87"/>
-      <c r="D37" s="91" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="91"/>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
-      <c r="I37" s="27"/>
-    </row>
-    <row r="38" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="I38" s="27"/>
-    </row>
-    <row r="39" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="87" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="87"/>
-      <c r="D39" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="I39" s="27"/>
-    </row>
-    <row r="40" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="56"/>
-      <c r="I40" s="27"/>
-    </row>
-    <row r="41" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C41" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F41" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I41" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" s="41" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="7" t="e">
-        <f>G42/F42*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I42" s="31" t="e">
-        <f>IF(H42&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" s="41" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="40" t="s">
-        <v>151</v>
-      </c>
-      <c r="C43" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="7" t="e">
-        <f>G43/F43*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I43" s="31" t="e">
-        <f>IF(H43&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="44" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="57"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="I44" s="27"/>
-    </row>
-    <row r="45" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="C45" s="84"/>
-      <c r="D45" s="85" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" s="86"/>
-      <c r="F45" s="86"/>
-      <c r="G45" s="86"/>
-      <c r="I45" s="27"/>
-    </row>
-    <row r="46" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="89"/>
-      <c r="C46" s="89"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="I46" s="27"/>
-    </row>
-    <row r="47" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H47" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I47" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" s="41" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="C48" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="30"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="7" t="e">
-        <f>G48/F48*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I48" s="31" t="e">
-        <f>IF(H48&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="49" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I49" s="27"/>
-    </row>
-    <row r="50" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="90" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="91" t="s">
-        <v>120</v>
-      </c>
-      <c r="E50" s="91"/>
-      <c r="F50" s="91"/>
-      <c r="G50" s="91"/>
-      <c r="I50" s="27"/>
-    </row>
-    <row r="51" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="56"/>
-      <c r="G51" s="56"/>
-      <c r="I51" s="27"/>
-    </row>
-    <row r="52" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" s="90"/>
-      <c r="D52" s="88" t="s">
-        <v>146</v>
-      </c>
-      <c r="E52" s="88"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
-      <c r="I52" s="27"/>
-    </row>
-    <row r="53" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="56"/>
-      <c r="G53" s="56"/>
-      <c r="I53" s="27"/>
-    </row>
-    <row r="54" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D54" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E54" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F54" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H54" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I54" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" s="49" customFormat="1" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="C55" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="50"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="7" t="e">
-        <f>G55/F55*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="31" t="e">
-        <f>IF(H55&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="56" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="56"/>
-      <c r="G56" s="56"/>
-      <c r="I56" s="27"/>
-    </row>
-    <row r="57" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="C57" s="90"/>
-      <c r="D57" s="65" t="s">
-        <v>139</v>
-      </c>
-      <c r="E57" s="65"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
-      <c r="I57" s="27"/>
-    </row>
-    <row r="58" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="56"/>
-      <c r="G58" s="56"/>
-      <c r="I58" s="27"/>
-    </row>
-    <row r="59" spans="2:9" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C59" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="I59" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="60" spans="2:9" ht="24" x14ac:dyDescent="0.25">
-      <c r="B60" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="D60" s="50"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="7" t="e">
-        <f>G60/F60*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I60" s="31" t="e">
-        <f>IF(H60&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="61" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="I61" s="27"/>
-    </row>
-    <row r="62" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="92" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="92"/>
-      <c r="D62" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
-      <c r="I62" s="27"/>
-    </row>
-    <row r="63" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="56"/>
-      <c r="C63" s="56"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="56"/>
-      <c r="F63" s="56"/>
-      <c r="G63" s="56"/>
-      <c r="I63" s="27"/>
-    </row>
-    <row r="64" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" s="92"/>
-      <c r="D64" s="65" t="s">
-        <v>143</v>
-      </c>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="65"/>
-      <c r="I64" s="27"/>
-    </row>
-    <row r="65" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="56"/>
-      <c r="C65" s="56"/>
-      <c r="D65" s="56"/>
-      <c r="E65" s="56"/>
-      <c r="F65" s="56"/>
-      <c r="G65" s="56"/>
-      <c r="I65" s="27"/>
-    </row>
-    <row r="66" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="C66" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="D66" s="46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E66" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="H66" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="I66" s="51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C67" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" s="30"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="48"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="7" t="e">
-        <f>G67/F67*100</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="31" t="e">
-        <f>IF(H67&gt;=50,"CONSIDERAR","NO")</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="68" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="116" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="117" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="118" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="119" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="121" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="122" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="123" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="124" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="125" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="126" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="127" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="128" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="129" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="130" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="131" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="132" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="135" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="137" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="138" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="139" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="140" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="141" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="142" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="161" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="162" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="163" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="164" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="165" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="166" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="167" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="168" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="169" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="170" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="171" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="172" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="173" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="174" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="175" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="176" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="177" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="178" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="179" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="180" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="181" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="182" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="184" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="185" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="186" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="187" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="188" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="189" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="190" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="191" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="192" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="193" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="194" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="195" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="196" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="197" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="198" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="199" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="200" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="201" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="202" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="203" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="204" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="205" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="206" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="207" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="208" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="209" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="210" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="211" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="212" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="213" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="214" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="215" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="216" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="217" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="218" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="219" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="220" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="221" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="222" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="223" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="224" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="225" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="226" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="227" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="228" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="229" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="230" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="231" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="232" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="233" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="234" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="235" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="236" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="237" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="238" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="239" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="240" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="241" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="242" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="243" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="244" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="245" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="246" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="247" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="248" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="249" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="250" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="251" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="252" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="253" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="254" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="255" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="256" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="257" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="258" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="259" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="260" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="261" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="262" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="263" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="264" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="265" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="266" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="267" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="268" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="269" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="270" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="271" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="272" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="273" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="274" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="275" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="276" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="277" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="278" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="279" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="280" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="281" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="282" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="283" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="284" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="285" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="286" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="287" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="288" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="289" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="290" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="291" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="292" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="293" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="294" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="295" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="296" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="297" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="298" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="299" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="300" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="301" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="302" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="303" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="304" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="305" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="306" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="307" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="308" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="309" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="310" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="311" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="312" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="313" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="314" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="315" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="316" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="317" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="318" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="319" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="320" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="321" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="322" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="323" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="324" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="325" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="326" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="327" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="328" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="329" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="330" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="331" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="332" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="333" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="334" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="335" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="336" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="337" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="338" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="339" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="340" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="341" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="342" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="343" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="344" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="345" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="346" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="347" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="348" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="349" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="350" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="351" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="352" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="353" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="354" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="355" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="356" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="357" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="358" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="359" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="360" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="361" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="362" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="363" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="364" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="365" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="366" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="367" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="368" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="369" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="370" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="371" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="372" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="373" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="374" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="375" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="376" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="377" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="378" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="379" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="380" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="381" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="382" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="383" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="384" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="385" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="386" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="387" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="388" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="389" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="390" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="391" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="392" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="393" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="394" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="395" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="396" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="397" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="398" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="399" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="400" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="401" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="402" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="403" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="404" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="405" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="406" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="407" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="408" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="409" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="410" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="411" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="412" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="413" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="414" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="415" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="416" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="417" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="418" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="419" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="420" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="421" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="422" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="423" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="424" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="425" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="426" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="427" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="428" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="429" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="430" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="431" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="432" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="433" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="434" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="435" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="436" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="437" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="438" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="439" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="440" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="441" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="442" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="443" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="444" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="445" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="446" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="447" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="448" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="449" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="450" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="451" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="452" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="453" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="454" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="455" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="456" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="457" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="458" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="459" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="460" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="461" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="462" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="463" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="464" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="465" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="466" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="467" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="468" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="469" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="470" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="471" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="472" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="473" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="474" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="475" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="476" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="477" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="478" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="479" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="480" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="481" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="482" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="483" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="484" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="485" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="486" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="487" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="488" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="489" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="490" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="491" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="492" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="493" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="494" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="495" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="496" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="497" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="498" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="499" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="500" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="501" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="502" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="503" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="504" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="505" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="506" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="507" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="508" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="509" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="510" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="511" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="512" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="513" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="514" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="515" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="516" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="517" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="518" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="519" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="520" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="521" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="522" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="523" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="524" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="525" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="526" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="527" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="528" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="529" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="530" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="531" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="532" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="533" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="534" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="535" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="536" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="537" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="538" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="543" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="544" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="545" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="546" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="547" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="548" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="549" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="550" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="551" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="552" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="553" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="554" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="555" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="556" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="557" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="558" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="559" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="560" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="561" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="562" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="563" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="564" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="565" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="566" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="567" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="568" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="569" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="570" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="571" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="572" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="573" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="574" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="575" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="576" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="577" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="578" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="579" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="580" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="581" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="582" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="583" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="584" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="585" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="586" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="587" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="588" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="589" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="590" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="591" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="592" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="593" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="594" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="595" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="596" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="597" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="598" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="599" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="600" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="601" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="602" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="603" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="604" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="605" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="606" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="607" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-  </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="P13:V13"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="P15:R15"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:G37"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:G39"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="B65:G65"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B56:G56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:G64"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H11">
     <cfRule type="cellIs" dxfId="53" priority="22" operator="lessThan">
@@ -10779,32 +10981,32 @@
       <c r="G1" s="8"/>
     </row>
     <row r="2" spans="2:13" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="109" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
     </row>
     <row r="3" spans="2:13" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
     </row>
     <row r="4" spans="2:13" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="99"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="101"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
       <c r="K4" s="14"/>
@@ -10812,37 +11014,37 @@
       <c r="M4" s="14"/>
     </row>
     <row r="5" spans="2:13" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
     </row>
     <row r="6" spans="2:13" s="2" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="103"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="107"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
-      <c r="K6" s="66" t="s">
+      <c r="K6" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="68"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="94"/>
     </row>
     <row r="7" spans="2:13" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="96"/>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
+      <c r="B7" s="95"/>
+      <c r="C7" s="95"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="95"/>
+      <c r="F7" s="95"/>
+      <c r="G7" s="95"/>
     </row>
     <row r="8" spans="2:13" s="1" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
@@ -11007,32 +11209,32 @@
       </c>
     </row>
     <row r="13" spans="2:13" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
+      <c r="B13" s="108"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
+      <c r="G13" s="108"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="2:13" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="105" t="s">
+      <c r="B14" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="107"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="108"/>
+      <c r="C14" s="104"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="112"/>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="2:13" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:13" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11117,32 +11319,32 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="96"/>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-      <c r="G19" s="96"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="95"/>
+      <c r="F19" s="95"/>
+      <c r="G19" s="95"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="105" t="s">
+      <c r="B20" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="105"/>
-      <c r="D20" s="101"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="103"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="107"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-      <c r="G21" s="96"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="95"/>
+      <c r="D21" s="95"/>
+      <c r="E21" s="95"/>
+      <c r="F21" s="95"/>
+      <c r="G21" s="95"/>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11203,44 +11405,44 @@
       <c r="A25" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="95"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="100"/>
+      <c r="C25" s="96"/>
+      <c r="D25" s="97"/>
+      <c r="E25" s="97"/>
+      <c r="F25" s="97"/>
+      <c r="G25" s="97"/>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="93"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="93"/>
-      <c r="F26" s="93"/>
-      <c r="G26" s="93"/>
-      <c r="H26" s="93"/>
+      <c r="B26" s="102"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="102"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="102"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="102"/>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="95" t="s">
+      <c r="B27" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="95"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
-      <c r="F27" s="100"/>
-      <c r="G27" s="100"/>
+      <c r="C27" s="96"/>
+      <c r="D27" s="97"/>
+      <c r="E27" s="97"/>
+      <c r="F27" s="97"/>
+      <c r="G27" s="97"/>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="96"/>
-      <c r="C28" s="96"/>
-      <c r="D28" s="96"/>
-      <c r="E28" s="96"/>
-      <c r="F28" s="96"/>
-      <c r="G28" s="96"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="95"/>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="95"/>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11325,32 +11527,32 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="104"/>
-      <c r="C32" s="104"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
+      <c r="B32" s="108"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="108"/>
+      <c r="G32" s="108"/>
       <c r="I32" s="2"/>
     </row>
     <row r="33" spans="2:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="105" t="s">
+      <c r="B33" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="105"/>
-      <c r="D33" s="100"/>
-      <c r="E33" s="100"/>
-      <c r="F33" s="100"/>
-      <c r="G33" s="100"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
       <c r="I33" s="2"/>
     </row>
     <row r="34" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="96"/>
+      <c r="B34" s="95"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="95"/>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
       <c r="I34" s="2"/>
     </row>
     <row r="35" spans="2:9" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11405,53 +11607,53 @@
       </c>
     </row>
     <row r="37" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="96"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="96"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="2:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="95" t="s">
+      <c r="B38" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="95"/>
-      <c r="D38" s="101"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="103"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="107"/>
       <c r="I38" s="2"/>
     </row>
     <row r="39" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="93"/>
-      <c r="C39" s="93"/>
-      <c r="D39" s="93"/>
-      <c r="E39" s="93"/>
-      <c r="F39" s="93"/>
-      <c r="G39" s="93"/>
-      <c r="H39" s="93"/>
+      <c r="B39" s="102"/>
+      <c r="C39" s="102"/>
+      <c r="D39" s="102"/>
+      <c r="E39" s="102"/>
+      <c r="F39" s="102"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="102"/>
       <c r="I39" s="2"/>
     </row>
     <row r="40" spans="2:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="101"/>
-      <c r="E40" s="102"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="103"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="106"/>
+      <c r="G40" s="107"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="96"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="96"/>
-      <c r="E41" s="96"/>
-      <c r="F41" s="96"/>
-      <c r="G41" s="96"/>
+      <c r="B41" s="95"/>
+      <c r="C41" s="95"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" ht="42.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11539,44 +11741,44 @@
       <c r="I45" s="2"/>
     </row>
     <row r="46" spans="2:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="95" t="s">
+      <c r="B46" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="C46" s="95"/>
-      <c r="D46" s="100"/>
-      <c r="E46" s="100"/>
-      <c r="F46" s="100"/>
-      <c r="G46" s="100"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="97"/>
+      <c r="E46" s="97"/>
+      <c r="F46" s="97"/>
+      <c r="G46" s="97"/>
       <c r="I46" s="2"/>
     </row>
     <row r="47" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="93"/>
-      <c r="C47" s="93"/>
-      <c r="D47" s="93"/>
-      <c r="E47" s="93"/>
-      <c r="F47" s="93"/>
-      <c r="G47" s="93"/>
-      <c r="H47" s="93"/>
+      <c r="B47" s="102"/>
+      <c r="C47" s="102"/>
+      <c r="D47" s="102"/>
+      <c r="E47" s="102"/>
+      <c r="F47" s="102"/>
+      <c r="G47" s="102"/>
+      <c r="H47" s="102"/>
       <c r="I47" s="2"/>
     </row>
     <row r="48" spans="2:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="95" t="s">
+      <c r="B48" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="95"/>
-      <c r="D48" s="109"/>
-      <c r="E48" s="109"/>
-      <c r="F48" s="109"/>
-      <c r="G48" s="109"/>
+      <c r="C48" s="96"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
       <c r="I48" s="2"/>
     </row>
     <row r="49" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="96"/>
-      <c r="C49" s="96"/>
-      <c r="D49" s="96"/>
-      <c r="E49" s="96"/>
-      <c r="F49" s="96"/>
-      <c r="G49" s="96"/>
+      <c r="B49" s="95"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="95"/>
+      <c r="E49" s="95"/>
+      <c r="F49" s="95"/>
+      <c r="G49" s="95"/>
       <c r="I49" s="2"/>
     </row>
     <row r="50" spans="2:9" ht="42.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11661,32 +11863,32 @@
       </c>
     </row>
     <row r="53" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="96"/>
-      <c r="C53" s="96"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="96"/>
-      <c r="F53" s="96"/>
-      <c r="G53" s="96"/>
+      <c r="B53" s="95"/>
+      <c r="C53" s="95"/>
+      <c r="D53" s="95"/>
+      <c r="E53" s="95"/>
+      <c r="F53" s="95"/>
+      <c r="G53" s="95"/>
       <c r="I53" s="2"/>
     </row>
     <row r="54" spans="2:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="95" t="s">
+      <c r="B54" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="95"/>
-      <c r="D54" s="100"/>
-      <c r="E54" s="100"/>
-      <c r="F54" s="100"/>
-      <c r="G54" s="100"/>
+      <c r="C54" s="96"/>
+      <c r="D54" s="97"/>
+      <c r="E54" s="97"/>
+      <c r="F54" s="97"/>
+      <c r="G54" s="97"/>
       <c r="I54" s="2"/>
     </row>
     <row r="55" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="96"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="96"/>
-      <c r="E55" s="96"/>
-      <c r="F55" s="96"/>
-      <c r="G55" s="96"/>
+      <c r="B55" s="95"/>
+      <c r="C55" s="95"/>
+      <c r="D55" s="95"/>
+      <c r="E55" s="95"/>
+      <c r="F55" s="95"/>
+      <c r="G55" s="95"/>
       <c r="I55" s="2"/>
     </row>
     <row r="56" spans="2:9" ht="42.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -11771,53 +11973,53 @@
       </c>
     </row>
     <row r="59" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="110"/>
-      <c r="C59" s="110"/>
-      <c r="D59" s="110"/>
-      <c r="E59" s="110"/>
-      <c r="F59" s="110"/>
-      <c r="G59" s="110"/>
+      <c r="B59" s="98"/>
+      <c r="C59" s="98"/>
+      <c r="D59" s="98"/>
+      <c r="E59" s="98"/>
+      <c r="F59" s="98"/>
+      <c r="G59" s="98"/>
       <c r="I59" s="2"/>
     </row>
     <row r="60" spans="2:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="95" t="s">
+      <c r="B60" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="C60" s="95"/>
-      <c r="D60" s="97"/>
-      <c r="E60" s="98"/>
-      <c r="F60" s="98"/>
-      <c r="G60" s="99"/>
+      <c r="C60" s="96"/>
+      <c r="D60" s="99"/>
+      <c r="E60" s="100"/>
+      <c r="F60" s="100"/>
+      <c r="G60" s="101"/>
       <c r="I60" s="2"/>
     </row>
     <row r="61" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="93"/>
-      <c r="C61" s="93"/>
-      <c r="D61" s="93"/>
-      <c r="E61" s="93"/>
-      <c r="F61" s="93"/>
-      <c r="G61" s="93"/>
-      <c r="H61" s="93"/>
+      <c r="B61" s="102"/>
+      <c r="C61" s="102"/>
+      <c r="D61" s="102"/>
+      <c r="E61" s="102"/>
+      <c r="F61" s="102"/>
+      <c r="G61" s="102"/>
+      <c r="H61" s="102"/>
       <c r="I61" s="2"/>
     </row>
     <row r="62" spans="2:9" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="95" t="s">
+      <c r="B62" s="96" t="s">
         <v>67</v>
       </c>
-      <c r="C62" s="95"/>
-      <c r="D62" s="97"/>
-      <c r="E62" s="98"/>
-      <c r="F62" s="98"/>
-      <c r="G62" s="99"/>
+      <c r="C62" s="96"/>
+      <c r="D62" s="99"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="100"/>
+      <c r="G62" s="101"/>
       <c r="I62" s="2"/>
     </row>
     <row r="63" spans="2:9" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="96"/>
-      <c r="C63" s="96"/>
-      <c r="D63" s="96"/>
-      <c r="E63" s="96"/>
-      <c r="F63" s="96"/>
-      <c r="G63" s="96"/>
+      <c r="B63" s="95"/>
+      <c r="C63" s="95"/>
+      <c r="D63" s="95"/>
+      <c r="E63" s="95"/>
+      <c r="F63" s="95"/>
+      <c r="G63" s="95"/>
       <c r="I63" s="2"/>
     </row>
     <row r="64" spans="2:9" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
@@ -12508,25 +12710,22 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="F/n4UgccRGgwPDul/QqmvdiOxgUsc2rdWgppWEKGQMTgRXQ1Iv133BiOUPSgtKvkUV5YPjHjEq97DU9Fk46vLA==" saltValue="d8qepB0E37z8AUHVwqwafg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="51">
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="B61:H61"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="B15:G15"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:G20"/>
@@ -12543,22 +12742,25 @@
     <mergeCell ref="B37:G37"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:G38"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="B26:H26"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="B61:H61"/>
   </mergeCells>
   <conditionalFormatting sqref="G9:G12">
     <cfRule type="cellIs" dxfId="29" priority="25" operator="lessThan">
@@ -12694,35 +12896,35 @@
       <c r="I1" s="3"/>
     </row>
     <row r="2" spans="2:12" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
+      <c r="L2" s="109"/>
     </row>
     <row r="3" spans="2:12" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="96"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
     </row>
     <row r="4" spans="2:12" ht="9.9499999999999993" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="95"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="95"/>
     </row>
     <row r="5" spans="2:12" s="1" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
@@ -12760,10 +12962,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="111" t="s">
+      <c r="B6" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="111" t="s">
+      <c r="C6" s="113" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -12781,19 +12983,19 @@
         <f>H6/G6*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J6" s="111" t="e">
+      <c r="J6" s="113" t="e">
         <f>SUM(I6:I9)/4</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K6" s="112" t="e">
+      <c r="K6" s="117" t="e">
         <f>SUM(J6:J12)/3</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="L6" s="113"/>
+      <c r="L6" s="114"/>
     </row>
     <row r="7" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="111"/>
-      <c r="C7" s="111"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="113"/>
       <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
@@ -12809,13 +13011,13 @@
         <f t="shared" ref="I7:I12" si="0">H7/G7*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J7" s="111"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="113"/>
+      <c r="J7" s="113"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="114"/>
     </row>
     <row r="8" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="113"/>
       <c r="D8" s="4" t="s">
         <v>33</v>
       </c>
@@ -12831,13 +13033,13 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J8" s="111"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="113"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="117"/>
+      <c r="L8" s="114"/>
     </row>
     <row r="9" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="111"/>
-      <c r="C9" s="111"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
       <c r="D9" s="4" t="s">
         <v>34</v>
       </c>
@@ -12853,13 +13055,13 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J9" s="111"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="113"/>
+      <c r="J9" s="113"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="114"/>
     </row>
     <row r="10" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="111"/>
-      <c r="C10" s="111" t="s">
+      <c r="B10" s="113"/>
+      <c r="C10" s="113" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -12877,16 +13079,16 @@
         <f>H10/G10*100</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J10" s="112" t="e">
+      <c r="J10" s="117" t="e">
         <f>SUM(I10:I11)/2</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K10" s="112"/>
-      <c r="L10" s="113"/>
+      <c r="K10" s="117"/>
+      <c r="L10" s="114"/>
     </row>
     <row r="11" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="111"/>
-      <c r="C11" s="111"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
       <c r="D11" s="4" t="s">
         <v>36</v>
       </c>
@@ -12902,12 +13104,12 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J11" s="112"/>
-      <c r="K11" s="112"/>
-      <c r="L11" s="113"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="114"/>
     </row>
     <row r="12" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="111"/>
+      <c r="B12" s="113"/>
       <c r="C12" s="4" t="s">
         <v>24</v>
       </c>
@@ -12929,14 +13131,14 @@
       <c r="J12" s="4">
         <v>62.5</v>
       </c>
-      <c r="K12" s="112"/>
-      <c r="L12" s="113"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="114"/>
     </row>
     <row r="13" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="111" t="s">
+      <c r="B13" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="111" t="s">
+      <c r="C13" s="113" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -12951,13 +13153,13 @@
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
-      <c r="J13" s="113"/>
-      <c r="K13" s="113"/>
-      <c r="L13" s="113"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="114"/>
     </row>
     <row r="14" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
       <c r="D14" s="4" t="s">
         <v>39</v>
       </c>
@@ -12970,12 +13172,12 @@
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
-      <c r="J14" s="113"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="113"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114"/>
     </row>
     <row r="15" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="111"/>
+      <c r="B15" s="113"/>
       <c r="C15" s="4" t="s">
         <v>27</v>
       </c>
@@ -12992,11 +13194,11 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-      <c r="K15" s="113"/>
-      <c r="L15" s="113"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114"/>
     </row>
     <row r="16" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="111" t="s">
+      <c r="B16" s="113" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -13015,11 +13217,11 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="114"/>
-      <c r="L16" s="113"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="114"/>
     </row>
     <row r="17" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="111"/>
+      <c r="B17" s="113"/>
       <c r="C17" s="4" t="s">
         <v>30</v>
       </c>
@@ -13036,14 +13238,14 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="113"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="114"/>
     </row>
     <row r="18" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="111" t="s">
+      <c r="B18" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="116" t="s">
+      <c r="C18" s="115" t="s">
         <v>44</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -13058,13 +13260,13 @@
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="113"/>
-      <c r="L18" s="113"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="114"/>
     </row>
     <row r="19" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="111"/>
-      <c r="C19" s="117"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="4" t="s">
         <v>48</v>
       </c>
@@ -13077,13 +13279,13 @@
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="113"/>
-      <c r="L19" s="113"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="114"/>
+      <c r="L19" s="114"/>
     </row>
     <row r="20" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="111"/>
-      <c r="C20" s="111" t="s">
+      <c r="B20" s="113"/>
+      <c r="C20" s="113" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -13098,13 +13300,13 @@
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="113"/>
-      <c r="L20" s="113"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="114"/>
     </row>
     <row r="21" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="111"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="4" t="s">
         <v>49</v>
       </c>
@@ -13117,15 +13319,15 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="113"/>
-      <c r="L21" s="113"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="114"/>
     </row>
     <row r="22" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="111" t="s">
+      <c r="B22" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="111" t="s">
+      <c r="C22" s="113" t="s">
         <v>51</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -13141,12 +13343,12 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
-      <c r="K22" s="113"/>
-      <c r="L22" s="113"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="114"/>
     </row>
     <row r="23" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="111"/>
-      <c r="C23" s="111"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="113"/>
       <c r="D23" s="9" t="s">
         <v>53</v>
       </c>
@@ -13160,12 +13362,12 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
-      <c r="K23" s="113"/>
-      <c r="L23" s="113"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="114"/>
     </row>
     <row r="24" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="111"/>
-      <c r="C24" s="111"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="113"/>
       <c r="D24" s="9" t="s">
         <v>54</v>
       </c>
@@ -13179,12 +13381,12 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
-      <c r="K24" s="113"/>
-      <c r="L24" s="113"/>
+      <c r="K24" s="114"/>
+      <c r="L24" s="114"/>
     </row>
     <row r="25" spans="2:12" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="111"/>
-      <c r="C25" s="111"/>
+      <c r="B25" s="113"/>
+      <c r="C25" s="113"/>
       <c r="D25" s="9" t="s">
         <v>55</v>
       </c>
@@ -13198,8 +13400,8 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="113"/>
+      <c r="K25" s="114"/>
+      <c r="L25" s="114"/>
     </row>
     <row r="26" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -13748,15 +13950,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="xC1V4yNK585/moy6zgzZEjjLCdKet5OJBASAFlunHYdh9485ZxRyBYtdd+hGd/XBNd+wAmfyVVdgWSfX4UGqWg==" saltValue="O+eCpiHfjEDumSRCXPqu7Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="25">
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="K22:K25"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="K18:K21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="J20:J21"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="D3:I3"/>
     <mergeCell ref="D4:I4"/>
@@ -13773,6 +13966,15 @@
     <mergeCell ref="K13:K15"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="K16:K17"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="K22:K25"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="K18:K21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="J20:J21"/>
   </mergeCells>
   <conditionalFormatting sqref="I6:I12">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
